--- a/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, referido por progenitor/a</t>
+          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,0; 37,76</t>
+          <t>32,34; 37,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,76; 36,04</t>
+          <t>30,0; 36,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27,9; 34,91</t>
+          <t>28,28; 35,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,4; 41,64</t>
+          <t>27,26; 41,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,94; 38,09</t>
+          <t>31,89; 38,17</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,2; 36,67</t>
+          <t>30,09; 36,86</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,88; 40,15</t>
+          <t>32,39; 39,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,85; 36,41</t>
+          <t>27,9; 36,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>32,66; 37,02</t>
+          <t>33,23; 37,22</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,06; 35,22</t>
+          <t>31,04; 35,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,6; 37,01</t>
+          <t>31,53; 36,72</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,7; 37,55</t>
+          <t>29,84; 37,42</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,09; 33,71</t>
+          <t>31,12; 33,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,7; 31,55</t>
+          <t>28,76; 31,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,79; 32,29</t>
+          <t>29,84; 32,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,4; 40,0</t>
+          <t>33,46; 40,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,77; 36,74</t>
+          <t>33,84; 36,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,58; 32,44</t>
+          <t>29,69; 32,44</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,04; 32,62</t>
+          <t>30,0; 32,78</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,49; 41,6</t>
+          <t>37,53; 41,54</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,88; 34,89</t>
+          <t>32,91; 34,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,61; 31,51</t>
+          <t>29,58; 31,59</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,26; 32,1</t>
+          <t>30,25; 32,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,1; 39,81</t>
+          <t>36,01; 39,79</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,31; 30,1</t>
+          <t>26,34; 30,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,35; 29,38</t>
+          <t>25,28; 29,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,74; 28,77</t>
+          <t>24,77; 28,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,37; 34,51</t>
+          <t>30,54; 34,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,4; 32,44</t>
+          <t>27,48; 32,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,52; 31,15</t>
+          <t>26,28; 30,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,05; 30,31</t>
+          <t>26,25; 30,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 37,29</t>
+          <t>32,77; 37,49</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,46; 30,7</t>
+          <t>27,48; 30,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,5; 29,56</t>
+          <t>26,56; 29,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,07; 29,11</t>
+          <t>26,09; 29,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,16; 35,61</t>
+          <t>32,31; 35,46</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,58; 32,7</t>
+          <t>30,74; 32,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,73; 30,91</t>
+          <t>28,72; 30,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,08; 31,15</t>
+          <t>29,07; 31,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,45; 38,4</t>
+          <t>33,32; 38,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,79; 35,17</t>
+          <t>32,83; 35,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,67; 31,84</t>
+          <t>29,63; 31,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,86; 31,96</t>
+          <t>29,94; 32,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,18; 39,47</t>
+          <t>36,38; 39,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,09; 33,71</t>
+          <t>32,11; 33,67</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,51; 31,11</t>
+          <t>29,56; 31,02</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,8; 31,25</t>
+          <t>29,82; 31,29</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,3; 38,21</t>
+          <t>35,3; 38,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,34; 37,89</t>
+          <t>31,91; 38,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30,0; 36,12</t>
+          <t>29,93; 36,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,28; 35,17</t>
+          <t>28,44; 35,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,26; 41,19</t>
+          <t>28,12; 41,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>31,89; 38,17</t>
+          <t>32,15; 38,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,09; 36,86</t>
+          <t>30,31; 36,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,39; 39,81</t>
+          <t>32,6; 40,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,9; 36,38</t>
+          <t>27,77; 36,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,23; 37,22</t>
+          <t>33,02; 37,33</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31,04; 35,67</t>
+          <t>30,89; 35,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,53; 36,72</t>
+          <t>31,49; 36,67</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,84; 37,42</t>
+          <t>29,77; 37,65</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,12; 33,8</t>
+          <t>31,1; 33,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,76; 31,45</t>
+          <t>28,82; 31,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,84; 32,35</t>
+          <t>29,74; 32,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,46; 40,47</t>
+          <t>33,45; 40,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,84; 36,82</t>
+          <t>33,57; 36,57</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,69; 32,44</t>
+          <t>29,67; 32,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,0; 32,78</t>
+          <t>29,86; 32,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,53; 41,54</t>
+          <t>37,2; 41,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,91; 34,99</t>
+          <t>32,85; 34,88</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,58; 31,59</t>
+          <t>29,6; 31,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,25; 32,1</t>
+          <t>30,2; 32,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,01; 39,79</t>
+          <t>36,08; 39,78</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,34; 30,16</t>
+          <t>26,11; 30,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,28; 29,43</t>
+          <t>25,59; 29,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,77; 28,88</t>
+          <t>24,83; 29,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,54; 34,72</t>
+          <t>30,52; 34,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,48; 32,54</t>
+          <t>27,59; 32,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,28; 30,92</t>
+          <t>26,44; 31,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,25; 30,59</t>
+          <t>26,16; 30,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,77; 37,49</t>
+          <t>32,73; 37,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,48; 30,44</t>
+          <t>27,3; 30,61</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,56; 29,69</t>
+          <t>26,54; 29,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,09; 29,11</t>
+          <t>26,15; 29,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,31; 35,46</t>
+          <t>32,31; 35,53</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,74; 32,8</t>
+          <t>30,67; 32,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,72; 30,82</t>
+          <t>28,74; 30,97</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,07; 31,1</t>
+          <t>29,11; 31,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,32; 38,92</t>
+          <t>33,32; 38,66</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,83; 35,19</t>
+          <t>32,76; 35,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,63; 31,93</t>
+          <t>29,68; 31,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,94; 32,09</t>
+          <t>29,84; 31,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,38; 39,59</t>
+          <t>36,28; 39,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,11; 33,67</t>
+          <t>32,02; 33,58</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,56; 31,02</t>
+          <t>29,56; 31,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,82; 31,29</t>
+          <t>29,76; 31,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,3; 38,29</t>
+          <t>35,34; 38,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34,92</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33,37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>35,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33,11</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>34,99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>32,9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>31,74</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36,31</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,92</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,37</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>35,94</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>31,98</t>
+          <t>38,9</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>33,99</t>
+          <t>35,69</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>31,91; 38,15</t>
+          <t>31,94; 38,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>29,93; 36,21</t>
+          <t>30,2; 36,67</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28,44; 35,22</t>
+          <t>32,88; 40,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28,12; 41,99</t>
+          <t>28,72; 37,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>32,15; 38,55</t>
+          <t>32,0; 37,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,31; 36,54</t>
+          <t>29,76; 36,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,6; 40,23</t>
+          <t>27,9; 34,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27,77; 36,44</t>
+          <t>34,52; 43,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>33,02; 37,33</t>
+          <t>32,66; 37,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,89; 35,44</t>
+          <t>31,06; 35,22</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,49; 36,67</t>
+          <t>31,6; 37,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>29,77; 37,65</t>
+          <t>32,54; 39,33</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>35,16</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>31,05</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>31,27</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>40,01</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>32,45</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>30,09</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>31,04</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>35,56</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>35,16</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>31,05</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>31,27</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39,35</t>
+          <t>35,02</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>37,58</t>
+          <t>37,66</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,1; 33,75</t>
+          <t>33,77; 36,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28,82; 31,52</t>
+          <t>29,58; 32,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29,74; 32,31</t>
+          <t>30,04; 32,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,45; 40,88</t>
+          <t>38,18; 42,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>33,57; 36,57</t>
+          <t>31,09; 33,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>29,67; 32,52</t>
+          <t>28,7; 31,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,86; 32,58</t>
+          <t>29,79; 32,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,2; 41,51</t>
+          <t>33,58; 36,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 34,88</t>
+          <t>32,88; 34,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29,6; 31,54</t>
+          <t>29,61; 31,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30,2; 32,06</t>
+          <t>30,26; 32,1</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,08; 39,78</t>
+          <t>36,45; 39,03</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>29,85</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28,63</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28,17</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35,79</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>28,14</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>27,34</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>26,82</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>32,49</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,85</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>28,63</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>28,17</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,94</t>
+          <t>33,14</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,8</t>
+          <t>34,51</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,11; 30,05</t>
+          <t>27,4; 32,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,59; 29,73</t>
+          <t>26,52; 31,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24,83; 29,04</t>
+          <t>26,05; 30,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,52; 34,61</t>
+          <t>33,63; 38,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>27,59; 32,54</t>
+          <t>26,31; 30,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,44; 31,04</t>
+          <t>25,35; 29,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,16; 30,32</t>
+          <t>24,74; 28,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>32,73; 37,56</t>
+          <t>31,02; 35,13</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>27,3; 30,61</t>
+          <t>27,46; 30,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26,54; 29,49</t>
+          <t>26,5; 29,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,15; 29,06</t>
+          <t>26,07; 29,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>32,31; 35,53</t>
+          <t>32,86; 36,32</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>33,98</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30,76</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>30,89</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38,48</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>31,68</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>29,79</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>30,09</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>34,92</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>30,76</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>37,73</t>
+          <t>34,85</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,42</t>
+          <t>36,77</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,67; 32,74</t>
+          <t>32,79; 35,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,74; 30,97</t>
+          <t>29,67; 31,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>29,11; 31,11</t>
+          <t>29,86; 31,96</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33,32; 38,66</t>
+          <t>36,9; 40,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>32,76; 35,15</t>
+          <t>30,58; 32,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,68; 31,98</t>
+          <t>28,73; 30,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,84; 31,96</t>
+          <t>29,08; 31,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>36,28; 39,49</t>
+          <t>33,71; 36,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>32,02; 33,58</t>
+          <t>32,09; 33,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29,56; 31,12</t>
+          <t>29,51; 31,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29,76; 31,2</t>
+          <t>29,8; 31,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>35,34; 38,09</t>
+          <t>35,81; 37,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IQ27-Estudios-trans_orig.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +140,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -526,7 +531,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso medio, en kilogramos, declarado por progenitor/a (tasa de respuesta: 96,01%)</t>
+          <t>Peso medio, en kilogramos, declarado por madres/padres (tasa de respuesta: 96,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -646,419 +651,271 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>34,92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33,37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>35,94</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>33,11</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,99</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,9</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>31,74</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>38,9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>34,96</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>33,13</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>33,93</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,69</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>34.92256686338035</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>33.37218826399738</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>35.93712420660623</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>33.10854970989576</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>34.99053849952519</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>32.90261273247923</v>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>31.73783075066678</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>38.90255844148022</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>34.95803885456346</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>33.1289694485723</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>33.93098452380964</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>35.68683547344337</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>31,94; 38,09</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30,2; 36,67</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>32,88; 40,15</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28,72; 37,78</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>32,0; 37,76</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>29,76; 36,04</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,9; 34,91</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>34,52; 43,46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>32,66; 37,02</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>31,06; 35,22</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31,6; 37,01</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>32,54; 39,33</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>31.93760448779955</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>30.20051106623024</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>32.8766285706339</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>28.71815412333369</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>31.99637178809117</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>29.76492690339496</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>27.90436005985847</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>34.52218700751021</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>32.6600580837836</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>31.05557322199826</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>31.59701463057319</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>32.53821940366493</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>38.08972819697304</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>36.66642464307688</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>40.1490295213141</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>37.78007326198195</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>37.76385338375506</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>36.04068207571517</v>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>34.91420246892091</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>43.45833794331018</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>37.02278686198714</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>35.22025436136795</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>37.01439430725696</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>39.32646478961291</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>35,16</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>31,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>31,27</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>40,01</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>32,45</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>30,09</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>31,04</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>35,02</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>33,91</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>30,59</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>31,16</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>37,66</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>33,77; 36,74</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29,58; 32,44</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30,04; 32,62</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38,18; 42,26</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>31,09; 33,71</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,7; 31,55</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>29,79; 32,29</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>33,58; 36,67</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>32,88; 34,89</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>29,61; 31,51</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>30,26; 32,1</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>36,45; 39,03</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>35.16335464238695</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>31.0498965950087</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>31.27096522995981</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>40.0103987700149</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>32.4506187450131</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>30.08596569187993</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>31.04455330711277</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>35.01973205835057</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>33.90535893313982</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>30.58655727181084</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>31.15840108175738</v>
+      </c>
+      <c r="N7" s="5" t="n">
+        <v>37.66476462179846</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>29,85</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>28,63</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>28,17</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>35,79</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>28,14</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>27,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>26,82</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33,14</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28,94</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27,99</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>27,53</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>34,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>33.77286183262355</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>29.58299315140651</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>30.03919157030727</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>38.17927127102183</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>31.09062688791867</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>28.70445492455222</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>29.79419259201135</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>33.57800172087169</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>32.88483788901331</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>29.61092774087986</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>30.25547831237622</v>
+      </c>
+      <c r="N8" s="5" t="n">
+        <v>36.45460223744426</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>27,4; 32,44</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>26,52; 31,15</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>26,05; 30,31</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>33,63; 38,18</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>26,31; 30,1</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>25,35; 29,38</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>24,74; 28,77</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>31,02; 35,13</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>27,46; 30,7</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>26,5; 29,56</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>26,07; 29,11</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>32,86; 36,32</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>36.7422652271047</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>32.43607099933661</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>32.62167314349333</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>42.25605414304368</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>33.70763044763957</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>31.55108987503527</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>32.28802316158201</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>36.66524218547712</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>34.89452368172412</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>31.51266433975762</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>32.09547097874535</v>
+      </c>
+      <c r="N9" s="5" t="n">
+        <v>39.03240017979046</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1066,137 +923,269 @@
           <t>Media</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>33,98</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30,76</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>30,89</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>38,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>31,68</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>29,79</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>30,09</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34,85</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>32,86</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>30,29</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>30,5</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>36,77</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>29.84757745920426</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>28.63274536985836</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>28.17067271123492</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>35.79320420170492</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>28.14095766561711</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>27.34128614471999</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>26.81907436268524</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>33.13859766635277</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>28.94360093304822</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>27.98875286465724</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>27.52770021863124</v>
+      </c>
+      <c r="N10" s="5" t="n">
+        <v>34.50533789470828</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>32,79; 35,17</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>29,67; 31,84</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>29,86; 31,96</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36,9; 40,17</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>30,58; 32,7</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>28,73; 30,91</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,08; 31,15</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>33,71; 36,09</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>32,09; 33,71</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>29,51; 31,11</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>29,8; 31,25</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>35,81; 37,82</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>27.40425697959213</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>26.5153081991596</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>26.05299160401093</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>33.634731256363</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>26.31230615444225</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>25.35105016887703</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>24.74104073862704</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>31.01861180320504</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>27.46402123312228</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>26.49821823908187</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>26.07236958948974</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>32.85799281114409</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>32.43759833426775</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>31.14626333608106</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>30.30726441956826</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>38.17523767003919</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>30.0972128562651</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>29.38427318756954</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>28.77117419133008</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>35.13241341347297</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>30.69838624928388</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>29.56169109638211</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>29.11327717121823</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>36.32143296470326</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>33.97858178118736</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>30.76219515419962</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>30.89386384577849</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>38.4777046442728</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>31.67946562434066</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>29.79499231024989</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>30.09099794967194</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>34.84815371302898</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>32.85958149250187</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>30.28887371256837</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>30.50029104602862</v>
+      </c>
+      <c r="N13" s="5" t="n">
+        <v>36.76589805336307</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>32.78986677199755</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>29.67342259469632</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>29.85555003947752</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>36.90430442148803</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>30.58184131401931</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>28.73098424343596</v>
+      </c>
+      <c r="I14" s="5" t="n">
+        <v>29.07987545762241</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>33.70843655391373</v>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>32.09322742954793</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>29.5077433081487</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>29.79823078815953</v>
+      </c>
+      <c r="N14" s="5" t="n">
+        <v>35.81199178808064</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>35.16910291854562</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>31.84410564524922</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>31.96246024512977</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>40.1687301002037</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>32.69639658263149</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>30.90687813639867</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>31.14784056787221</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>36.08720308140644</v>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>33.71374599789781</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>31.11468118452548</v>
+      </c>
+      <c r="M15" s="5" t="n">
+        <v>31.24508485558694</v>
+      </c>
+      <c r="N15" s="5" t="n">
+        <v>37.82033916001068</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1204,14 +1193,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
